--- a/ABAP Programming/OOPs.xlsx
+++ b/ABAP Programming/OOPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABAP 2026\ABAP Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9387AF87-B84A-4662-BAB0-56ECEC4923A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA1D9A-3F77-4001-AD62-AFAECF046AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>ZCL_STRUC_TABLE_COMBO</t>
   </si>
@@ -64,13 +64,67 @@
   </si>
   <si>
     <t>Progam Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritance </t>
+  </si>
+  <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Super Class Name</t>
+  </si>
+  <si>
+    <t>Sub Class Name</t>
+  </si>
+  <si>
+    <t>Z_INHERI_PRG_MY</t>
+  </si>
+  <si>
+    <t>ZCL_INHERITANCE_SUB</t>
+  </si>
+  <si>
+    <t>ZCL_INHERITANCE_SUPER</t>
+  </si>
+  <si>
+    <t>Abstract Class</t>
+  </si>
+  <si>
+    <t>ZABSTRACT_SUP</t>
+  </si>
+  <si>
+    <t>Parent Class</t>
+  </si>
+  <si>
+    <t>zabstract_sub1sr</t>
+  </si>
+  <si>
+    <t>Child Class</t>
+  </si>
+  <si>
+    <t>ZABSTRACT_SUB2SR</t>
+  </si>
+  <si>
+    <t>ZABSTRACT_PRG_MY</t>
+  </si>
+  <si>
+    <t>Abstract Class With Local</t>
+  </si>
+  <si>
+    <t>ZABSTRACT_LOCAL_MY</t>
+  </si>
+  <si>
+    <t>Exception Class</t>
+  </si>
+  <si>
+    <t>ZCX_EXCEPTION_MY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,8 +132,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -92,8 +160,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -125,17 +217,136 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -151,6 +362,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1188720</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>121921</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>485414</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>121921</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0977820-E180-2F8E-4138-0A8600E62E99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3931920" y="3048001"/>
+          <a:ext cx="10025654" cy="4754880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1280161</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>170329</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD62483-99E7-89A9-1B7F-14D73758202E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4014396" y="8518264"/>
+          <a:ext cx="9611957" cy="4032324"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,91 +720,973 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:Q74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.109375" customWidth="1"/>
+    <col min="15" max="15" width="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="K3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="16"/>
+      <c r="O3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="F4" t="s">
+      <c r="C4" s="14"/>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="K5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="K6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="13"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="K7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="O10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
+      <c r="O12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="D14" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="18"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="D16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+    </row>
+    <row r="17" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="18"/>
+    </row>
+    <row r="18" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="18"/>
+    </row>
+    <row r="19" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+    </row>
+    <row r="20" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+    </row>
+    <row r="21" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+    </row>
+    <row r="22" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+    </row>
+    <row r="23" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+    </row>
+    <row r="24" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+    </row>
+    <row r="25" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+    </row>
+    <row r="26" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+    </row>
+    <row r="27" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+    </row>
+    <row r="28" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+    </row>
+    <row r="29" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+    </row>
+    <row r="30" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+    </row>
+    <row r="31" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+    </row>
+    <row r="32" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+    </row>
+    <row r="33" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+    </row>
+    <row r="34" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+    </row>
+    <row r="35" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+    </row>
+    <row r="36" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+    </row>
+    <row r="37" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+    </row>
+    <row r="38" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+    </row>
+    <row r="39" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+    </row>
+    <row r="40" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+    </row>
+    <row r="41" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+    </row>
+    <row r="42" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+    </row>
+    <row r="43" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+    </row>
+    <row r="44" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+    </row>
+    <row r="45" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+    </row>
+    <row r="46" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+    </row>
+    <row r="47" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+    </row>
+    <row r="48" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+    </row>
+    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+    </row>
+    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+    </row>
+    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+    </row>
+    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+    </row>
+    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+    </row>
+    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+    </row>
+    <row r="55" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+    </row>
+    <row r="56" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+    </row>
+    <row r="57" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+    </row>
+    <row r="58" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+    </row>
+    <row r="59" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+    </row>
+    <row r="60" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+    </row>
+    <row r="61" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+    </row>
+    <row r="62" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+    </row>
+    <row r="63" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+    </row>
+    <row r="64" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+    </row>
+    <row r="65" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+    </row>
+    <row r="66" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+    </row>
+    <row r="67" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+    </row>
+    <row r="68" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+    </row>
+    <row r="69" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+    </row>
+    <row r="70" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+    </row>
+    <row r="71" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+    </row>
+    <row r="72" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+    </row>
+    <row r="73" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+    </row>
+    <row r="74" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="D16:N16"/>
+    <mergeCell ref="D14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>